--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260806.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>3.83%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
@@ -660,112 +660,112 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>46,121,000</t>
+          <t>5,972,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>5,972,000</t>
+          <t>46,121,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>35,274,000</t>
+          <t>9,790,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>20,089,000</t>
+          <t>21,105,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>9,790,000</t>
+          <t>35,274,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,66 +777,66 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>30,079,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>21,105,000</t>
+          <t>20,089,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>30,079,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -880,178 +880,178 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>11,165,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>11,165,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>9,520,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>3,284,309,231</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>20,683,000</t>
+          <t>9,520,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>33,782,000</t>
+          <t>20,683,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>3,104,872,569</t>
+          <t>33,782,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -1100,24 +1100,24 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,44 +1129,44 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>17,369,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -1188,73 +1188,73 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>17,369,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,481,625,322</t>
+          <t>9,574,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>9,574,000</t>
+          <t>2,448,145,322</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -1283,66 +1283,66 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,120,000</t>
+          <t>6,546,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>5,975,000</t>
+          <t>14,120,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>13,785,000</t>
+          <t>5,975,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1364,95 +1364,95 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>6,546,000</t>
+          <t>13,785,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>22,613,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>22,613,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1496,51 +1496,51 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,223,000</t>
+          <t>8,715,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>8,715,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1606,90 +1606,90 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1760,24 +1760,24 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>PB_NTD</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-6,727,758</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,22 +1789,22 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>PFUR_NTD</t>
+          <t>PB_NTD</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
+          <t>PAYABLES</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>-110,089,104</t>
+          <t>-16,304,964</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
     </row>
